--- a/outputs/42354.xlsx
+++ b/outputs/42354.xlsx
@@ -142,24 +142,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -415,139 +419,139 @@
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="24.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="70.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="1" width="24.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="70.5"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="e">
-        <f aca="false">#N/A</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C2" s="3" t="e">
-        <f aca="false">#N/A</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D2" s="4" t="str">
-        <f aca="false">IF(ISNA(A2),IF(ISNA(B2),IF(ISNA(C2),"",C2),B2),A2)</f>
+      <c r="B2" s="4" t="e">
+        <f aca="false">#N/A</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C2" s="4" t="e">
+        <f aca="false">#N/A</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D2" s="5" t="str">
+        <f aca="false">IFERROR(A2, IFERROR(B2, IFERROR(C2, "")))</f>
         <v>Completed</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="e">
-        <f aca="false">#N/A</f>
-        <v>#N/A</v>
-      </c>
-      <c r="B3" s="3" t="n">
+      <c r="A3" s="4" t="e">
+        <f aca="false">#N/A</f>
+        <v>#N/A</v>
+      </c>
+      <c r="B3" s="4" t="n">
         <v>44635</v>
       </c>
-      <c r="C3" s="3" t="e">
-        <f aca="false">#N/A</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <f aca="false">IF(ISNA(A3),IF(ISNA(B3),IF(ISNA(C3),"",C3),B3),A3)</f>
+      <c r="C3" s="4" t="e">
+        <f aca="false">#N/A</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <f aca="false">IFERROR(A3, IFERROR(B3, IFERROR(C3, "")))</f>
         <v>44635</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="e">
-        <f aca="false">#N/A</f>
-        <v>#N/A</v>
-      </c>
-      <c r="B4" s="3" t="e">
-        <f aca="false">#N/A</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="A4" s="4" t="e">
+        <f aca="false">#N/A</f>
+        <v>#N/A</v>
+      </c>
+      <c r="B4" s="4" t="e">
+        <f aca="false">#N/A</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="4" t="str">
-        <f aca="false">IF(ISNA(A4),IF(ISNA(B4),IF(ISNA(C4),"",C4),B4),A4)</f>
+      <c r="D4" s="5" t="str">
+        <f aca="false">IFERROR(A4, IFERROR(B4, IFERROR(C4, "")))</f>
         <v>ENR</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="4" t="n">
         <v>44304</v>
       </c>
-      <c r="C5" s="3" t="e">
-        <f aca="false">#N/A</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D5" s="4" t="str">
-        <f aca="false">IF(ISNA(A5),IF(ISNA(B5),IF(ISNA(C5),"",C5),B5),A5)</f>
+      <c r="C5" s="4" t="e">
+        <f aca="false">#N/A</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D5" s="5" t="str">
+        <f aca="false">IFERROR(A5, IFERROR(B5, IFERROR(C5, "")))</f>
         <v>Completed</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="e">
-        <f aca="false">#N/A</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="B6" s="4" t="e">
+        <f aca="false">#N/A</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="4" t="str">
-        <f aca="false">IF(ISNA(A6),IF(ISNA(B6),IF(ISNA(C6),"",C6),B6),A6)</f>
+      <c r="D6" s="5" t="str">
+        <f aca="false">IFERROR(A6, IFERROR(B6, IFERROR(C6, "")))</f>
         <v>Completed</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="e">
-        <f aca="false">#N/A</f>
-        <v>#N/A</v>
-      </c>
-      <c r="B7" s="3" t="n">
+      <c r="A7" s="4" t="e">
+        <f aca="false">#N/A</f>
+        <v>#N/A</v>
+      </c>
+      <c r="B7" s="4" t="n">
         <v>43713</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="4" t="n">
-        <f aca="false">IF(ISNA(A7),IF(ISNA(B7),IF(ISNA(C7),"",C7),B7),A7)</f>
+      <c r="D7" s="5" t="n">
+        <f aca="false">IFERROR(A7, IFERROR(B7, IFERROR(C7, "")))</f>
         <v>43713</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="e">
-        <f aca="false">#N/A</f>
-        <v>#N/A</v>
-      </c>
-      <c r="B8" s="3" t="e">
-        <f aca="false">#N/A</f>
-        <v>#N/A</v>
-      </c>
-      <c r="C8" s="3" t="e">
-        <f aca="false">#N/A</f>
-        <v>#N/A</v>
-      </c>
-      <c r="D8" s="4" t="str">
-        <f aca="false">IF(ISNA(A8),IF(ISNA(B8),IF(ISNA(C8),"",C8),B8),A8)</f>
+      <c r="A8" s="4" t="e">
+        <f aca="false">#N/A</f>
+        <v>#N/A</v>
+      </c>
+      <c r="B8" s="4" t="e">
+        <f aca="false">#N/A</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C8" s="4" t="e">
+        <f aca="false">#N/A</f>
+        <v>#N/A</v>
+      </c>
+      <c r="D8" s="5" t="str">
+        <f aca="false">IFERROR(A8, IFERROR(B8, IFERROR(C8, "")))</f>
         <v/>
       </c>
     </row>

--- a/outputs/42354.xlsx
+++ b/outputs/42354.xlsx
@@ -451,7 +451,7 @@
         <v>#N/A</v>
       </c>
       <c r="D2" s="5" t="str">
-        <f aca="false">IFERROR(A2, IFERROR(B2, IFERROR(C2, "")))</f>
+        <f aca="false">IF(ISNA(A2),IF(ISNA(B2),IF(ISNA(C2),"",C2),B2),A2)</f>
         <v>Completed</v>
       </c>
     </row>
@@ -468,7 +468,7 @@
         <v>#N/A</v>
       </c>
       <c r="D3" s="5" t="n">
-        <f aca="false">IFERROR(A3, IFERROR(B3, IFERROR(C3, "")))</f>
+        <f aca="false">IF(ISNA(A3),IF(ISNA(B3),IF(ISNA(C3),"",C3),B3),A3)</f>
         <v>44635</v>
       </c>
     </row>
@@ -485,7 +485,7 @@
         <v>5</v>
       </c>
       <c r="D4" s="5" t="str">
-        <f aca="false">IFERROR(A4, IFERROR(B4, IFERROR(C4, "")))</f>
+        <f aca="false">IF(ISNA(A4),IF(ISNA(B4),IF(ISNA(C4),"",C4),B4),A4)</f>
         <v>ENR</v>
       </c>
     </row>
@@ -501,7 +501,7 @@
         <v>#N/A</v>
       </c>
       <c r="D5" s="5" t="str">
-        <f aca="false">IFERROR(A5, IFERROR(B5, IFERROR(C5, "")))</f>
+        <f aca="false">IF(ISNA(A5),IF(ISNA(B5),IF(ISNA(C5),"",C5),B5),A5)</f>
         <v>Completed</v>
       </c>
     </row>
@@ -517,7 +517,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="5" t="str">
-        <f aca="false">IFERROR(A6, IFERROR(B6, IFERROR(C6, "")))</f>
+        <f aca="false">IF(ISNA(A6),IF(ISNA(B6),IF(ISNA(C6),"",C6),B6),A6)</f>
         <v>Completed</v>
       </c>
     </row>
@@ -533,7 +533,7 @@
         <v>5</v>
       </c>
       <c r="D7" s="5" t="n">
-        <f aca="false">IFERROR(A7, IFERROR(B7, IFERROR(C7, "")))</f>
+        <f aca="false">IF(ISNA(A7),IF(ISNA(B7),IF(ISNA(C7),"",C7),B7),A7)</f>
         <v>43713</v>
       </c>
     </row>
@@ -551,7 +551,7 @@
         <v>#N/A</v>
       </c>
       <c r="D8" s="5" t="str">
-        <f aca="false">IFERROR(A8, IFERROR(B8, IFERROR(C8, "")))</f>
+        <f aca="false">IF(ISNA(A8),IF(ISNA(B8),IF(ISNA(C8),"",C8),B8),A8)</f>
         <v/>
       </c>
     </row>
